--- a/APRESENTAÇÃO SIMULAÇÕES/DRE-Sao Bernardo-Sao Caetano-NALATA.xlsx
+++ b/APRESENTAÇÃO SIMULAÇÕES/DRE-Sao Bernardo-Sao Caetano-NALATA.xlsx
@@ -757,43 +757,43 @@
         <v>16</v>
       </c>
       <c r="B3" s="6">
-        <v>7236</v>
+        <v>6728</v>
       </c>
       <c r="C3" s="6">
-        <v>8442</v>
+        <v>7850</v>
       </c>
       <c r="D3" s="6">
-        <v>10050</v>
+        <v>9345</v>
       </c>
       <c r="E3" s="6">
-        <v>11658</v>
+        <v>10840</v>
       </c>
       <c r="F3" s="6">
-        <v>13668</v>
+        <v>12709</v>
       </c>
       <c r="G3" s="6">
-        <v>16080</v>
+        <v>14952</v>
       </c>
       <c r="H3" s="6">
-        <v>18492</v>
+        <v>17195</v>
       </c>
       <c r="I3" s="6">
-        <v>21708</v>
+        <v>20185</v>
       </c>
       <c r="J3" s="6">
-        <v>25326</v>
+        <v>23549</v>
       </c>
       <c r="K3" s="6">
-        <v>29748</v>
+        <v>27661</v>
       </c>
       <c r="L3" s="6">
-        <v>34572</v>
+        <v>32147</v>
       </c>
       <c r="M3" s="6">
-        <v>40200</v>
+        <v>37380</v>
       </c>
       <c r="N3" s="6">
-        <v>237180</v>
+        <v>220541</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -933,43 +933,43 @@
         <v>20</v>
       </c>
       <c r="B8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="C8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="D8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="G8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="L8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M8" s="6">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="N8" s="6">
-        <v>8400</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1065,43 +1065,43 @@
         <v>23</v>
       </c>
       <c r="B11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="C11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M11" s="6">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N11" s="6">
-        <v>4800</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1153,43 +1153,43 @@
         <v>25</v>
       </c>
       <c r="B13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="C13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="D13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="E13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="F13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="G13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="H13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="I13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="J13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="K13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="L13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="M13" s="9">
-        <v>6689.51</v>
+        <v>6489.51</v>
       </c>
       <c r="N13" s="9">
-        <v>80274.12</v>
+        <v>77874.12000000001</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1549,43 +1549,43 @@
         <v>34</v>
       </c>
       <c r="B24" s="12">
-        <v>14155.51</v>
+        <v>13955.51</v>
       </c>
       <c r="C24" s="12">
-        <v>14236.51</v>
+        <v>14036.51</v>
       </c>
       <c r="D24" s="12">
-        <v>14335.51</v>
+        <v>14135.51</v>
       </c>
       <c r="E24" s="12">
-        <v>14443.51</v>
+        <v>14243.51</v>
       </c>
       <c r="F24" s="12">
-        <v>19278.510000000002</v>
+        <v>19078.510000000002</v>
       </c>
       <c r="G24" s="12">
-        <v>19431.510000000002</v>
+        <v>19231.510000000002</v>
       </c>
       <c r="H24" s="12">
-        <v>19611.510000000002</v>
+        <v>19411.510000000002</v>
       </c>
       <c r="I24" s="12">
-        <v>20958.510000000002</v>
+        <v>20758.510000000002</v>
       </c>
       <c r="J24" s="12">
-        <v>21891.510000000002</v>
+        <v>21691.510000000002</v>
       </c>
       <c r="K24" s="12">
-        <v>24019.510000000002</v>
+        <v>23819.510000000002</v>
       </c>
       <c r="L24" s="12">
-        <v>24582.510000000002</v>
+        <v>24382.510000000002</v>
       </c>
       <c r="M24" s="12">
-        <v>25429.510000000002</v>
+        <v>25229.510000000002</v>
       </c>
       <c r="N24" s="12">
-        <v>232374.12000000005</v>
+        <v>229974.12000000005</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -1637,43 +1637,43 @@
         <v>36</v>
       </c>
       <c r="B27" s="14">
-        <v>-6919.51</v>
+        <v>-7227.51</v>
       </c>
       <c r="C27" s="14">
-        <v>-5794.51</v>
+        <v>-6186.51</v>
       </c>
       <c r="D27" s="14">
-        <v>-4285.51</v>
+        <v>-4790.51</v>
       </c>
       <c r="E27" s="14">
-        <v>-2785.51</v>
+        <v>-3403.51</v>
       </c>
       <c r="F27" s="14">
-        <v>-5610.510000000002</v>
+        <v>-6369.510000000002</v>
       </c>
       <c r="G27" s="14">
-        <v>-3351.510000000002</v>
+        <v>-4279.510000000002</v>
       </c>
       <c r="H27" s="14">
-        <v>-1119.510000000002</v>
-      </c>
-      <c r="I27" s="15">
-        <v>749.489999999998</v>
+        <v>-2216.510000000002</v>
+      </c>
+      <c r="I27" s="14">
+        <v>-573.510000000002</v>
       </c>
       <c r="J27" s="15">
-        <v>3434.489999999998</v>
+        <v>1857.489999999998</v>
       </c>
       <c r="K27" s="15">
-        <v>5728.489999999998</v>
+        <v>3841.489999999998</v>
       </c>
       <c r="L27" s="15">
-        <v>9989.489999999998</v>
+        <v>7764.489999999998</v>
       </c>
       <c r="M27" s="15">
-        <v>14770.489999999998</v>
-      </c>
-      <c r="N27" s="15">
-        <v>4805.879999999983</v>
+        <v>12150.489999999998</v>
+      </c>
+      <c r="N27" s="14">
+        <v>-9433.120000000017</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -1681,43 +1681,43 @@
         <v>37</v>
       </c>
       <c r="B28" s="14">
-        <v>-6919.51</v>
+        <v>-7227.51</v>
       </c>
       <c r="C28" s="14">
-        <v>-12714.02</v>
+        <v>-13414.02</v>
       </c>
       <c r="D28" s="14">
-        <v>-16999.53</v>
+        <v>-18204.53</v>
       </c>
       <c r="E28" s="14">
-        <v>-19785.04</v>
+        <v>-21608.04</v>
       </c>
       <c r="F28" s="14">
-        <v>-25395.550000000003</v>
+        <v>-27977.550000000003</v>
       </c>
       <c r="G28" s="14">
-        <v>-28747.060000000005</v>
+        <v>-32257.060000000005</v>
       </c>
       <c r="H28" s="14">
-        <v>-29866.570000000007</v>
+        <v>-34473.57000000001</v>
       </c>
       <c r="I28" s="14">
-        <v>-29117.08000000001</v>
+        <v>-35047.08000000001</v>
       </c>
       <c r="J28" s="14">
-        <v>-25682.59000000001</v>
+        <v>-33189.59000000001</v>
       </c>
       <c r="K28" s="14">
-        <v>-19954.100000000013</v>
+        <v>-29348.100000000013</v>
       </c>
       <c r="L28" s="14">
-        <v>-9964.610000000015</v>
-      </c>
-      <c r="M28" s="15">
-        <v>4805.879999999983</v>
-      </c>
-      <c r="N28" s="15">
-        <v>4805.879999999983</v>
+        <v>-21583.610000000015</v>
+      </c>
+      <c r="M28" s="14">
+        <v>-9433.120000000017</v>
+      </c>
+      <c r="N28" s="14">
+        <v>-9433.120000000017</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
